--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technical Architect - Platform - Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56ba0f8432c551e</t>
+          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Reporting &amp; Analytics Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Reporting &amp; Analytics Developer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Engineer with Genie</t>
+          <t>Technical Solutions Architect II -- Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Solutions Architect II -- Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Clinic System Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>University of the Pacific</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Backend Engineer, Toolbox Diagnostics, Vehicle Software</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bfc6b63a12e6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
+          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54759aa3ffee8233</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=54759aa3ffee8233</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BH Management Services, LLC</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Node.js Connectivity Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tech Savants</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b17ca5e720295d3</t>
+          <t>https://www.indeed.com/viewjob?jk=35f46c60eb5eb938</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f46c60eb5eb938</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Scala, Kafka, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8b5d8e5fb610b3</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Sr. ERP Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>IP Corporation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect - Senior</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Time Travel, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. ERP Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IP Corporation</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Solution Architect - Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
+          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Systems Reliability Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Security Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20b04f614c47a99</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7139ab3ddc5daefd</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior Software Developer, Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>O'Fallon, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615774aaccc3425f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Kafka, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,19 +4171,19 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>Software Engineer (Sr. Software Engineer, DOE)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PurpleLab</t>
+          <t>foureyes</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d467b6c089b449b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fc0f4840ee51ac</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Application Engineer, Cyber Security</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Inmar</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=111703762ff5efcb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,19 +4311,19 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,19 +4451,19 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mid/Senior Full Stack Java Developer (w/ experience in UI/UX and Angular Testing Frameworks_</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kaizen Solutions Group</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf534b4f57bf0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ffdcc3ef0b5287</t>
+          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer (Sr. Software Engineer, DOE)</t>
+          <t>Senior Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>foureyes</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fc0f4840ee51ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Application Engineer, Cyber Security</t>
+          <t>Senior Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Inmar</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4660,356 +4660,6 @@
         </is>
       </c>
       <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=111703762ff5efcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sr Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Kiewit Corporation</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Developer / AI Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>PARKWOOD</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer Java · Spring Boot · Connected Services</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11fd47c28958a887</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>QA Engineer - Gen AI</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Sustainment</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Everforth ECS</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Full stack Developer (Java - React JS)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Med-Metrix</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Med-Metrix</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=224f644ff51634b1</t>
         </is>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,12 +923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technical Architect - ML</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Rhythm Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clinic System Administrator</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>University of the Pacific</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4ef185557a4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ACCO Engineered Systems</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>ACCO Engineered Systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Owl Labs</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7383687e3e9016</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Owl Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71d06adc0eea81c</t>
+          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Owl Labs</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0230aad2426cbb0e</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54759aa3ffee8233</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f46c60eb5eb938</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Sr. ERP Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>IP Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8296d590972dce</t>
+          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Solution Architect - Senior</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1401c985416eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. ERP Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IP Corporation</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solution Architect - Senior</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025e476a43fdb23a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer (Sr. Software Engineer, DOE)</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>foureyes</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fc0f4840ee51ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Application Engineer, Cyber Security</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Inmar</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111703762ff5efcb</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
+          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>QA Engineer - Gen AI</t>
+          <t>Software Engineer (Sr. Software Engineer, DOE)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sustainment</t>
+          <t>foureyes</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fc0f4840ee51ac</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Engineer, Cyber Security</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Inmar</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=111703762ff5efcb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Senior Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4625,41 +4625,6 @@
         </is>
       </c>
       <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Med-Metrix</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=224f644ff51634b1</t>
         </is>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant – Modern Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6194bf1cf11624a3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Reporting &amp; Analytics Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Reporting &amp; Analytics Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Engineer with Genie</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Solutions Architect II -- Data Engineer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Solutions Architect II -- Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Database Administrator (Senior)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rhythm Energy</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Architect - ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rhythm Energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ACCO Engineered Systems</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>ACCO Engineered Systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
+          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. ERP Developer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IP Corporation</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solution Architect - Senior</t>
+          <t>Sr. ERP Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>IP Corporation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
+          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Solution Architect - Senior</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
+          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>QA Engineer - Gen AI</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sustainment</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer (Sr. Software Engineer, DOE)</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>foureyes</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Git, CloudWatch, Datadog, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fc0f4840ee51ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Application Engineer, Cyber Security</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Inmar</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111703762ff5efcb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,42 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc0e618cf1de443</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Med-Metrix</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=224f644ff51634b1</t>
+          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, GCP, BigQuery, Dataflow, Vertex AI</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Reporting &amp; Analytics Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Reporting &amp; Analytics Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Engineer with Genie</t>
+          <t>Technical Solutions Architect II -- Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Solutions Architect II -- Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Database Administrator (Senior)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Administrator (Senior)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>Medlytix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Spark, Kafka, Polars, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
+          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ACCO Engineered Systems</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>ACCO Engineered Systems</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
+          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a49d7ee8cbacdd</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>MedaSync LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Sr. ERP Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>IP Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. ERP Developer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IP Corporation</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solution Architect - Senior</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b20c7e930af523</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, MongoDB, NoSQL, ELT, MLOps, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bcd8bc3a260293</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>QA Engineer - Gen AI</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sustainment</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4555,41 +4555,6 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Veritone</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Consultant – Modern Data &amp; Analytics Engineering</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6194bf1cf11624a3</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Reporting &amp; Analytics Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Reporting &amp; Analytics Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>BSF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>Branson, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Elizabethtown, KY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d703a95f6d98132d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43612f69ee01f601</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MedaSync LLC</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97d1ff01dd6d447</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Senior Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>A2Z Sync</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. ERP Developer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IP Corporation</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Sr. ERP Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>IP Corporation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,19 +4451,19 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>QA Engineer - Gen AI</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sustainment</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,15 +4546,85 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>QA Engineer - Gen AI</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sustainment</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Veritone</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Solutions Architect II -- Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
+          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Database Administrator (Senior)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Administrator (Senior)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>Medlytix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Spark, Kafka, Polars, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
+          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medlytix</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Spark, Kafka, Polars, dbt</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Rhythm Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rhythm Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
         </is>
       </c>
     </row>
@@ -1063,52 +1063,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=762c612b9070e685</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ACCO Engineered Systems</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164fac28ad1ee39b</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,217 +1851,217 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,137 +2526,137 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>New York Technology Partners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a9d26d08938e9d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Veeva Vault Technical Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Senior Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>A2Z Sync</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A2Z Sync</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24be73dfc99f77ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Power BI, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. ERP Developer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IP Corporation</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131d87174c52388</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,77 +3426,77 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da96aab1eec7799c</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Search Platform (Data Ingestion)</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8e62ba93d8b1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,252 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Full stack Developer (Java - React JS)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Database Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Database Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>AEP/CDP Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Bounteous</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>QA Engineer - Gen AI</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Sustainment</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Veritone</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52067741848b2d5c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Reporting &amp; Analytics Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Reporting &amp; Analytics Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Senior Advisor – Data Engineering/Snowflake (Austin, TX)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BSF</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
+          <t>https://www.indeed.com/viewjob?jk=e215e6f2072e7561</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Engineer with Genie</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BSF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Administrator (Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
+          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medlytix</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Spark, Kafka, Polars, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Database Administrator (Senior)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Medlytix</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Spark, Kafka, Polars, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Aries Computer Systems, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rhythm Energy</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a225f0dc6b137ec</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Technical Architect - ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Rhythm Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762c612b9070e685</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=762c612b9070e685</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MongoDB, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d313a335c0aa8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New York Technology Partners</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a9d26d08938e9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer MS Fabric</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7a49c864b47f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Veeva Vault Technical Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A2Z Sync</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, DynamoDB</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>26-3103: Senior Full Stack Software Developer - Herndon, VA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>Navitas Business Consulting</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab3a7cf7327a053</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Veeva Vault Technical Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>A2Z Sync</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,102 +3506,102 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VulcanForms Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Devens, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Brown University Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373009b5b8e87f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Cloud Architect - Product Owner</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4cddfc2bfc8bbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ccf381e23c9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c20b3e1f2e260a</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,147 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AEP/CDP Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Bounteous</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3beae28e28fda3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc5fe80e753160</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>QA Engineer - Gen AI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Sustainment</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Reporting &amp; Analytics Developer</t>
+          <t>Senior Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce520836a7b20db</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor – Data Engineering/Snowflake (Austin, TX)</t>
+          <t>Senior Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e215e6f2072e7561</t>
+          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BSF</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
+          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Engineer with Genie</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BSF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,104 +731,104 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Administrator (Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medlytix</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Spark, Kafka, Polars, dbt</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d805ab0f62ca63</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Database Administrator (Senior)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aries Computer Systems, Inc.</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195228dfb1b62318</t>
+          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technical Architect - ML</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Hybrid Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
+          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
+          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Temporary - Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762c612b9070e685</t>
+          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=762c612b9070e685</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Integration Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McNees Wallace &amp; Nurick</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,94 +2036,94 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Scala, Snowflake, Oracle, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2848b54f8fe7f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer MS Fabric</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7a49c864b47f5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer III, Cloud SDET - Platform (Hybrid)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7108583ab9e8178</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer MS Fabric</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7a49c864b47f5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26-3103: Senior Full Stack Software Developer - Herndon, VA</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Navitas Business Consulting</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab3a7cf7327a053</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Veeva Vault Technical Developer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI/ML</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A2Z Sync</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c35bec2870d92f</t>
+          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Backend</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>26-3103: Senior Full Stack Software Developer - Herndon, VA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>Navitas Business Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab3a7cf7327a053</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Veeva Vault Technical Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,102 +3191,102 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Santa Clara Valley Transportation Authority</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior Site Reliability Engineer - Workflow Automation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Wizards)</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Monumental Sports &amp; Entertainment</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, GCP, Scala, dbt, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VulcanForms Inc.</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Devens, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, RDS, Scala, Terraform</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf53288277c169e</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Brown University Health</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Brown University Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Architect - Product Owner</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
+          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Architect - Product Owner</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f5edd185e9397</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb719e56f139219</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Developer / AI Engineer</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PARKWOOD</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Integrations Engineer</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,87 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>QA Engineer - Gen AI</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Sustainment</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rhythm Energy</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d93d722cff256d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technical Architect - ML</t>
+          <t>Senior Hybrid Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Hybrid Infrastructure Engineer</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
+          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51a0ab8752890e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99526482fb3f2596</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762c612b9070e685</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,182 +1851,182 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b206c836b146d886</t>
+          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Specialist-Cloud &amp; Infra Engg</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, IAM, RDS, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb757e0cec50dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f106f4aef3387bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer MS Fabric</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,147 +2656,147 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7a49c864b47f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer MS Fabric</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7a49c864b47f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>26-3103: Senior Full Stack Software Developer - Herndon, VA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Navitas Business Consulting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260c5053550dcc93</t>
+          <t>https://www.indeed.com/viewjob?jk=1ab3a7cf7327a053</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Veeva Vault Technical Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Software Engineer II, Backend</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454bb52747a889f0</t>
+          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II, Backend</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26-3103: Senior Full Stack Software Developer - Herndon, VA</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Navitas Business Consulting</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab3a7cf7327a053</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Veeva Vault Technical Developer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Point Predictive</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Seaboard Energy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Merriam, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,94 +3226,94 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Full-stack Swift Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Administrator</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Santa Clara Valley Transportation Authority</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b324f909786d78d0</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Johnston, IA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Workflow Automation</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c56c74489218e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,77 +3636,77 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,129 +3716,129 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Sequoia Financial Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>IAM, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8a63fd992df921e9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Med-Metrix</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Vertex AI, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Brown University Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Cloud Architect - Product Owner</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Brown University Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Architect - Product Owner</t>
+          <t>QA Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sustainment</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3995,181 +3995,6 @@
         </is>
       </c>
       <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>AssistRx</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Eko Green Industrial</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Miami Lakes, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe1f0ce627c9867</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>QA Engineer - Gen AI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Sustainment</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
         </is>

--- a/results/job_matches_2026-08-05.xlsx
+++ b/results/job_matches_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (contract)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Oozie, YARN, Impala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
+          <t>https://www.indeed.com/viewjob?jk=e283799e17891679</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27dbaa3dc8a3b601</t>
+          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer(Python)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BSF</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>BSF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Engineer with Genie</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Benchmark Solutions LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Databricks Engineer with Genie</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
+          <t>https://www.indeed.com/viewjob?jk=c37120edd193930a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
+          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer - NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9fb5b732c3b1248</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Administrator (Senior)</t>
+          <t>Full Stack Python Developer - NJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b79dc3572aa8d5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Database Administrator (Senior)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c3a516ffdf929</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Full Stack Java with Angular - Onsite - Atlanta/Alpharetta</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=476324ac0bfc1988</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technical Architect - ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Hybrid Infrastructure Engineer</t>
+          <t>Technical Architect - ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Databricks, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ddac9e239bbef4c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Hybrid Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Quality Engineer - Automation Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
+          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
+          <t>https://www.indeed.com/viewjob?jk=fff37e48506ad994</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>MO 85- Power BI and Data engineer (806590)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Fellowship Health Resources, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>ITgen systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Andes, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Engineer I,II,III, SR</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tinker Federal Credit Union</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
+          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Database Engineer I,II,III, SR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>Tinker Federal Credit Union</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=24c1d9b0ab8147e7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
+          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Kafka SRE Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
+          <t>https://www.indeed.com/viewjob?jk=27df3f02572cf962</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
+          <t>https://www.indeed.com/viewjob?jk=7343ee7d85121f7f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f99e68d0187163</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=53383e166b43fdd7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
+          <t>https://www.indeed.com/viewjob?jk=701373d80e74128d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbe0a0577aa5f10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a2c0ca7ef648062d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer MS Fabric</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,112 +2656,112 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7a49c864b47f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b33bdfcd561be9b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L3)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
+          <t>https://www.indeed.com/viewjob?jk=47bb1952df61e19f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9403b57a174788</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f54ef1af497100</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce4f903ab0e9bd9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e96d806ef18289e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>26-3103: Senior Full Stack Software Developer - Herndon, VA</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Navitas Business Consulting</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab3a7cf7327a053</t>
+          <t>https://www.indeed.com/viewjob?jk=d174a62833050e13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Veeva Vault Technical Developer</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5964c3554c1268</t>
+          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II, Backend</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer (L3)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=ff134c7c98fad31c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Cloud/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460176c0aae0f7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Johnston, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Software Engineer II, Backend</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=41fd173dde7ceb58</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE)</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Seaboard Energy</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Merriam, KS, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4a17716151df0</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-stack Swift Developer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full-stack Swift Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Full-stack Swift Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Capital Markets Technology</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,129 +3716,129 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfc8bfc31bb2a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sequoia Financial Group</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a63fd992df921e9</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23da33ff41d6d3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Scientist- Generative AI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Brown University Health</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Sequoia Financial Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=8a63fd992df921e9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cloud Architect - Product Owner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Oracle Fusion Senior Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f70d46bede5c9eb5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>QA Engineer - Gen AI</t>
+          <t>Oracle Fusion Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sustainment</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,192 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, MLOps, MLflow, CI/CD, Kubernetes, pytest</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caa8a2e6fc3e9671</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>IT Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Brown University Health</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Providence, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Cloud Architect - Product Owner</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ab9dc066eafbe44</t>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>AssistRx</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Eko Green Industrial</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Miami Lakes, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
